--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.026833</v>
+        <v>0.245986</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.245986</v>
+        <v>0.575478</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.575478</v>
+        <v>-0.487466</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.487466</v>
+        <v>0.029334</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.029334</v>
+        <v>-0.013543</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.013543</v>
+        <v>-1.464645</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.464645</v>
+        <v>-0.501009</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.501009</v>
+        <v>-2.245492</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -437,7 +437,7 @@
         <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>1.578075</v>
+        <v>1.53102</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.527203</v>
+        <v>-0.577389</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>3.039018</v>
+        <v>3.101037</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.778386</v>
+        <v>-1.83747</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>5.816157</v>
+        <v>5.888577</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>2.621877</v>
+        <v>2.551692</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>-2.046989</v>
+        <v>-1.923866</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>-3.488194</v>
+        <v>-3.609353</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.094751</v>
+        <v>-1.921089</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.283684</v>
+        <v>-2.456705</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.841907</v>
+        <v>-2.081801</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.942552</v>
+        <v>-3.139842</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.594081</v>
+        <v>-1.872012</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>6.730239</v>
+        <v>6.417995</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>4.221074</v>
+        <v>4.593353</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>6.033964</v>
+        <v>5.656557</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>-5.213785</v>
+        <v>-4.809539</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>7.660341</v>
+        <v>7.203139</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>1.071609</v>
+        <v>1.528694</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.316514</v>
+        <v>-1.76079</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>-2.179339</v>
+        <v>-1.756709</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>2.571445</v>
+        <v>2.130195</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.63918</v>
+        <v>-0.233442</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>-4.648642</v>
+        <v>-5.076558</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>7.418429</v>
+        <v>6.869947</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>2.66472</v>
+        <v>2.196256</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>1.192283</v>
+        <v>1.653504</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.678821</v>
+        <v>-1.12946</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.131808</v>
+        <v>0.30756</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>8.393212999999999</v>
+        <v>7.918429</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>3.337242</v>
+        <v>3.855867</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>1.374705</v>
+        <v>0.86847</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>0.20664</v>
+        <v>0.718937</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>4.244535</v>
+        <v>3.714306</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>2.773544</v>
+        <v>4.166499</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>5.706153</v>
+        <v>5.214425</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>3.876937</v>
+        <v>3.380467</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>-2.968997</v>
+        <v>-3.35722</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.046295</v>
+        <v>-0.602183</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>6.971704</v>
+        <v>6.493752</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>0.864002</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>10.081782</v>
+        <v>9.629631</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>5.834506</v>
+        <v>6.286027</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.487144</v>
+        <v>-0.909891</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>0.167229</v>
+        <v>0.571621</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.036424</v>
+        <v>-0.438371</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>5.480991</v>
+        <v>6.768497</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>10.567985</v>
+        <v>10.156134</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>3.681522</v>
+        <v>3.183416</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>5.92888</v>
+        <v>6.465655</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>2.543686</v>
+        <v>2.025904</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>8.976785</v>
+        <v>9.306397</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>10.959081</v>
+        <v>10.59619</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>-11.144248</v>
+        <v>-11.438858</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.70789</v>
+        <v>-0.387297</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.174512</v>
+        <v>-0.790567</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>-11.788183</v>
+        <v>-12.072719</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,7 @@
         <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>0.651276</v>
+        <v>1.696174</v>
       </c>
     </row>
     <row r="60">
@@ -901,7 +901,7 @@
         <v>46265</v>
       </c>
       <c r="B60" t="n">
-        <v>9.434195000000001</v>
+        <v>9.118577999999999</v>
       </c>
     </row>
     <row r="61">
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.245492</v>
+        <v>-3.396189</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.396189</v>
+        <v>-2.334042</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.334042</v>
+        <v>-1.584291</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.584291</v>
+        <v>-2.019413</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.019413</v>
+        <v>-1.262972</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.262972</v>
+        <v>-2.126516</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.126516</v>
+        <v>-2.543791</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.543791</v>
+        <v>-2.577262</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.577262</v>
+        <v>-3.704117</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.704117</v>
+        <v>-4.074531</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-4.074531</v>
+        <v>-4.132549</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-4.132549</v>
+        <v>-3.896019</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.896019</v>
+        <v>-3.576923</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.576923</v>
+        <v>-6.932951</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.932951</v>
+        <v>-6.941874</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.941874</v>
+        <v>-6.647326</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.647326</v>
+        <v>-6.607165</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.607165</v>
+        <v>-6.475515</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.475515</v>
+        <v>-6.520143</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -434,482 +434,482 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>1.53102</v>
+        <v>-0.577389</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.577389</v>
+        <v>3.101037</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>3.101037</v>
+        <v>-1.83747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.83747</v>
+        <v>5.888577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>5.888577</v>
+        <v>2.551692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>2.551692</v>
+        <v>-1.923866</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.923866</v>
+        <v>-3.609353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>-3.609353</v>
+        <v>-1.921089</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.921089</v>
+        <v>-2.456705</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.456705</v>
+        <v>-2.081801</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.081801</v>
+        <v>-3.139842</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>-3.139842</v>
+        <v>-1.872012</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.872012</v>
+        <v>6.417995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>6.417995</v>
+        <v>4.593353</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>4.593353</v>
+        <v>5.656557</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>5.656557</v>
+        <v>-4.809539</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>-4.809539</v>
+        <v>7.203139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>7.203139</v>
+        <v>1.528694</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>1.528694</v>
+        <v>-1.76079</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.76079</v>
+        <v>-1.756709</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.756709</v>
+        <v>2.130195</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>2.130195</v>
+        <v>-0.233442</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.233442</v>
+        <v>-5.076558</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>-5.076558</v>
+        <v>6.869947</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>6.869947</v>
+        <v>2.196256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>2.196256</v>
+        <v>1.653504</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>1.653504</v>
+        <v>-1.12946</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.12946</v>
+        <v>0.30756</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>0.30756</v>
+        <v>7.918429</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>7.918429</v>
+        <v>3.855867</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>3.855867</v>
+        <v>0.86847</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>0.86847</v>
+        <v>0.718937</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>0.718937</v>
+        <v>3.714306</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>3.714306</v>
+        <v>4.166499</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>4.166499</v>
+        <v>5.214425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>5.214425</v>
+        <v>3.380467</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>3.380467</v>
+        <v>-3.35722</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>-3.35722</v>
+        <v>-0.602183</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.602183</v>
+        <v>6.493752</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>6.493752</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>1.28</v>
+        <v>9.629631</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>9.629631</v>
+        <v>6.286027</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>6.286027</v>
+        <v>-0.909891</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.909891</v>
+        <v>0.571621</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>0.571621</v>
+        <v>-0.438371</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.438371</v>
+        <v>6.768497</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>6.768497</v>
+        <v>10.156134</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>10.156134</v>
+        <v>3.183416</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>3.183416</v>
+        <v>6.465655</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>6.465655</v>
+        <v>2.025904</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>2.025904</v>
+        <v>9.306397</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>9.306397</v>
+        <v>10.59619</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>10.59619</v>
+        <v>-11.438858</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>-11.438858</v>
+        <v>-0.387297</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.387297</v>
+        <v>-0.790567</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.790567</v>
+        <v>-12.072719</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>-12.072719</v>
+        <v>1.696174</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>1.696174</v>
+        <v>9.118577999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>9.118577999999999</v>
+        <v>-6.57815</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-6.520143</v>
+        <v>0.207794</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.207794</v>
+        <v>-0.6281870000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.6281870000000001</v>
+        <v>-0.752383</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.752383</v>
+        <v>-0.582807</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.582807</v>
+        <v>-0.470542</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.470542</v>
+        <v>0.109862</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.109862</v>
+        <v>-1.225316</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.225316</v>
+        <v>-0.936303</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.936303</v>
+        <v>-0.6879</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.6879</v>
+        <v>0.578014</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.578014</v>
+        <v>0.654451</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.654451</v>
+        <v>0.706991</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.706991</v>
+        <v>0.040598</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.040598</v>
+        <v>0.126587</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.126587</v>
+        <v>-0.222139</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.222139</v>
+        <v>-1.636133</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.636133</v>
+        <v>-1.466558</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.466558</v>
+        <v>-0.145702</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.145702</v>
+        <v>0.503968</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.503968</v>
+        <v>-0.133759</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.133759</v>
+        <v>-0.592359</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.592359</v>
+        <v>-0.415611</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.415611</v>
+        <v>-0.898084</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.898084</v>
+        <v>-2.804121</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.804121</v>
+        <v>-4.213346</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-4.213346</v>
+        <v>-4.270673</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-4.270673</v>
+        <v>-3.675929</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.675929</v>
+        <v>-2.732466</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.732466</v>
+        <v>-3.224502</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.224502</v>
+        <v>-3.802522</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,482 +434,474 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.577389</v>
+        <v>3.101037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B3" t="n">
-        <v>3.101037</v>
+        <v>-1.83747</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.83747</v>
+        <v>5.888577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>5.888577</v>
+        <v>2.551692</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B6" t="n">
-        <v>2.551692</v>
+        <v>-1.923866</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.923866</v>
+        <v>-3.609353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B8" t="n">
-        <v>-3.609353</v>
+        <v>-1.921089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.921089</v>
+        <v>-2.456705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.456705</v>
+        <v>-2.081801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.081801</v>
+        <v>-3.139842</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B12" t="n">
-        <v>-3.139842</v>
+        <v>-1.872012</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.872012</v>
+        <v>6.417995</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B14" t="n">
-        <v>6.417995</v>
+        <v>4.593353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B15" t="n">
-        <v>4.593353</v>
+        <v>5.656557</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B16" t="n">
-        <v>5.656557</v>
+        <v>-4.809539</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>-4.809539</v>
+        <v>7.203139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B18" t="n">
-        <v>7.203139</v>
+        <v>1.528694</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B19" t="n">
-        <v>1.528694</v>
+        <v>-1.76079</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.76079</v>
+        <v>-1.756709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.756709</v>
+        <v>2.130195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B22" t="n">
-        <v>2.130195</v>
+        <v>-0.233442</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.233442</v>
+        <v>-5.076558</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B24" t="n">
-        <v>-5.076558</v>
+        <v>6.869947</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B25" t="n">
-        <v>6.869947</v>
+        <v>2.196256</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B26" t="n">
-        <v>2.196256</v>
+        <v>1.653504</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B27" t="n">
-        <v>1.653504</v>
+        <v>-1.12946</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.12946</v>
+        <v>0.30756</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B29" t="n">
-        <v>0.30756</v>
+        <v>7.918429</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B30" t="n">
-        <v>7.918429</v>
+        <v>3.855867</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B31" t="n">
-        <v>3.855867</v>
+        <v>0.86847</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B32" t="n">
-        <v>0.86847</v>
+        <v>0.718937</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B33" t="n">
-        <v>0.718937</v>
+        <v>3.714306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B34" t="n">
-        <v>3.714306</v>
+        <v>4.166499</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B35" t="n">
-        <v>4.166499</v>
+        <v>5.214425</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B36" t="n">
-        <v>5.214425</v>
+        <v>3.380467</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B37" t="n">
-        <v>3.380467</v>
+        <v>-3.35722</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B38" t="n">
-        <v>-3.35722</v>
+        <v>-0.602183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.602183</v>
+        <v>6.493752</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B40" t="n">
-        <v>6.493752</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B41" t="n">
-        <v>1.28</v>
+        <v>9.629631</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B42" t="n">
-        <v>9.629631</v>
+        <v>6.286027</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>6.286027</v>
+        <v>-0.909891</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.909891</v>
+        <v>0.571621</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B45" t="n">
-        <v>0.571621</v>
+        <v>-0.438371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.438371</v>
+        <v>6.768497</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B47" t="n">
-        <v>6.768497</v>
+        <v>10.156134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B48" t="n">
-        <v>10.156134</v>
+        <v>3.183416</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B49" t="n">
-        <v>3.183416</v>
+        <v>6.465655</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B50" t="n">
-        <v>6.465655</v>
+        <v>2.025904</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B51" t="n">
-        <v>2.025904</v>
+        <v>9.306397</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B52" t="n">
-        <v>9.306397</v>
+        <v>10.59619</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B53" t="n">
-        <v>10.59619</v>
+        <v>-11.438858</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B54" t="n">
-        <v>-11.438858</v>
+        <v>-0.387297</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.387297</v>
+        <v>-0.790567</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.790567</v>
+        <v>-12.072719</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B57" t="n">
-        <v>-12.072719</v>
+        <v>1.696174</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B58" t="n">
-        <v>1.696174</v>
+        <v>9.118577999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B59" t="n">
-        <v>9.118577999999999</v>
+        <v>-6.57815</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B60" t="n">
-        <v>-6.57815</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B61" t="n">
-        <v>-3.802522</v>
+        <v>-6.704569</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_ouro.xlsx
+++ b/data/final/series/yahoo_ret_ouro.xlsx
@@ -901,7 +901,7 @@
         <v>46326</v>
       </c>
       <c r="B60" t="n">
-        <v>-6.704569</v>
+        <v>-6.874156</v>
       </c>
     </row>
   </sheetData>
